--- a/MINI PROJECT/3IST01_Mini Project Details.xlsx
+++ b/MINI PROJECT/3IST01_Mini Project Details.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
   <si>
     <t>SI.NO</t>
   </si>
@@ -803,9 +803,6 @@
     <t>G1 Canteen Management</t>
   </si>
   <si>
-    <t>Library Module</t>
-  </si>
-  <si>
     <t>G3-Student Intranet</t>
   </si>
   <si>
@@ -821,21 +818,12 @@
     <t>G7-Admission Mgmt</t>
   </si>
   <si>
-    <t>CAUGHT WITH MOBILE PHONE  G8-Enrollment mgmt</t>
-  </si>
-  <si>
     <t>G9 (Placement Management)</t>
   </si>
   <si>
     <t>G10- Hostel Mgmt</t>
   </si>
   <si>
-    <t>G11- Alumni</t>
-  </si>
-  <si>
-    <t>G12- HRMS</t>
-  </si>
-  <si>
     <t>20251LIT3001</t>
   </si>
   <si>
@@ -858,13 +846,102 @@
   </si>
   <si>
     <t>4, 18</t>
+  </si>
+  <si>
+    <t>Objective</t>
+  </si>
+  <si>
+    <t>The objective of the Canteen Management website is to digitize and streamline food ordering, billing, and inventory operations within the campus. It allows students, faculty, and staff to order meals online, view menus, make cashless payments, and track order status in real time.
+Administrators can manage food items, update prices, monitor stock levels, and analyze sales reports for efficient resource planning.
+The ultimate goal is to provide convenience, transparency, and operational efficiency in canteen services while reducing manual errors and waiting times.</t>
+  </si>
+  <si>
+    <t>The Library Management website aims to automate book cataloging, issuing, and return processes to enhance accessibility for students and staff.
+Users can search for books, reserve titles, check availability, and view due dates online. Librarians can manage book inventories, maintain digital records, and generate reports.
+The objective is to promote a digital, user-friendly library environment that reduces manual workload and ensures the timely circulation of learning resources.</t>
+  </si>
+  <si>
+    <t>The Students’ Intranet website acts as a digital communication hub for students and faculty, enabling collaboration and information sharing within the institution.
+It includes discussion forums, announcements, academic updates, and peer-to-peer networking features.
+The goal is to foster a connected campus community, improve communication efficiency, and promote knowledge exchange through a secure internal network.</t>
+  </si>
+  <si>
+    <t>The Course Management website is designed to organize, deliver, and track academic courses for both instructors and students.
+It allows faculty to upload lectures, assignments, and assessments, while students can access study materials, submit work, and monitor progress.
+The objective is to provide a centralized e-learning platform that enhances academic management, improves transparency, and supports blended learning.</t>
+  </si>
+  <si>
+    <t>The Student Management website focuses on maintaining comprehensive student records including personal details, academic progress, attendance, and performance.
+Administrators can manage admissions, track attendance, and evaluate students' progress in real time.
+The objective is to create a single unified system for student data management that simplifies administrative tasks and supports data-driven decision-making.</t>
+  </si>
+  <si>
+    <t>The Fees Management website aims to automate fee collection, receipt generation, and financial tracking within the institution.
+Students can pay fees online, view payment history, and download receipts. Administrators can monitor pending dues, send alerts, and generate reports.
+The key objective is to ensure financial transparency, minimize errors, and offer a convenient, cashless payment system.</t>
+  </si>
+  <si>
+    <t>The Admission Management website is designed to digitize the student admission process — from application submission to enrollment confirmation.
+It allows applicants to apply online, upload documents, check admission status, and receive notifications.
+Administrators can verify applications, shortlist candidates, and manage seat allocation efficiently.
+The objective is to make admissions faster, paperless, and error-free, reducing manual workload and improving applicant experience.</t>
+  </si>
+  <si>
+    <t>The Enrollment Management website aims to simplify and automate the process of course enrollment and registration for students in an academic institution.
+It enables students to log in securely, view available courses, check prerequisites, select subjects, and enroll within a specific timeline.
+Faculty and administrators can manage course capacities, monitor enrollments, and generate reports on student registration trends.
+The website also integrates with other systems (like Student Management and Course Management) to ensure data consistency across modules.
+The main objective is to provide a transparent, error-free, and efficient enrollment process that minimizes manual intervention, avoids duplication, and enhances student satisfaction through real-time updates and confirmations.</t>
+  </si>
+  <si>
+    <t>The Placement Management website’s objective is to bridge the gap between students and recruiters through a digital platform.
+Students can create profiles, upload resumes, and apply for jobs, while companies can post vacancies and schedule interviews.
+Placement officers can manage drives, track student participation, and maintain placement records.
+The main goal is to ensure smooth coordination between students, recruiters, and placement cells with data transparency.</t>
+  </si>
+  <si>
+    <t>The Hostel Management website aims to automate room allocation, fee management, and grievance tracking for hostel residents.
+Students can apply for rooms, check availability, and pay hostel fees online. Wardens can assign rooms, track occupancy, and maintain discipline records.
+The objective is to ensure organized accommodation management, enhance communication between residents and wardens, and improve overall hostel administration.</t>
+  </si>
+  <si>
+    <t>The Alumni Management website facilitates ongoing engagement between alumni and the institution.
+It allows alumni to register, share updates, post job opportunities, and participate in events.
+Administrators can manage alumni databases and organize reunions or mentorship programs.
+The key objective is to strengthen the alumni network, promote collaboration, and encourage contributions to the institution’s growth.</t>
+  </si>
+  <si>
+    <t>The HRMS-Recruitment Management website is designed to manage faculty and staff recruitment, attendance, payroll, and performance evaluations.
+It allows applicants to apply for jobs, upload resumes, and track status, while HR personnel can schedule interviews and manage records digitally.
+The main objective is to build a centralized HR portal that ensures efficiency, reduces paperwork, and supports transparent recruitment and employee management.</t>
+  </si>
+  <si>
+    <t>The objective of the HRMS–Recruitment Management website is to digitally transform the entire employee lifecycle, from job posting and recruitment to onboarding and performance management.
+It provides a centralized web platform where candidates can apply for open positions, upload resumes, and track their application status, while HR administrators can manage job listings, schedule interviews, evaluate applicants, and issue offer letters—all in one integrated system.
+Beyond recruitment, the HRMS also handles employee record management, attendance tracking, leave approvals, and performance reviews, ensuring all HR operations are transparent and efficient.
+The website reduces paperwork, enhances collaboration among HR teams, and maintains a secure database of employee information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  G8-Enrollment mgmt</t>
+  </si>
+  <si>
+    <t>G11- Alumni Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G12- HRMS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">G13- HRMS </t>
+  </si>
+  <si>
+    <t>G2 Library Module</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -882,12 +959,6 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -912,7 +983,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -922,18 +993,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -950,7 +1009,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1010,15 +1069,213 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1028,52 +1285,102 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1362,1374 +1669,1420 @@
     <col min="3" max="3" width="17.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="48.28515625" customWidth="1"/>
+    <col min="8" max="8" width="79.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="2">
+      <c r="H5" s="43" t="s">
+        <v>273</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="29">
         <v>1</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
+      <c r="H6" s="44" t="s">
+        <v>274</v>
+      </c>
+      <c r="I6" s="42"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="2">
+      <c r="B7" s="32">
         <v>2</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="42"/>
     </row>
     <row r="8" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="14">
+      <c r="B8" s="34">
         <v>3</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="2">
+      <c r="G8" s="40"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="42"/>
+    </row>
+    <row r="9" spans="2:9" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="32">
         <v>4</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="2">
+      <c r="G9" s="40"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="42"/>
+    </row>
+    <row r="10" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="36">
         <v>5</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="42"/>
     </row>
     <row r="11" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="2">
+      <c r="B11" s="27">
         <v>6</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>275</v>
+      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="1">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="2:9" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="1">
+        <v>10</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="4">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="2">
-        <v>7</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="H16" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="1">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17" s="15"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="15"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="15"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="16"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="1">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="4">
+        <v>17</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="15"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="1">
+        <v>18</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="1">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="15"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="1">
+        <v>20</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G25" s="16"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="1">
+        <v>21</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="I26" s="3"/>
+    </row>
+    <row r="27" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B27" s="1">
+        <v>22</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" s="15"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="3"/>
+    </row>
+    <row r="28" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" s="1">
+        <v>23</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" s="15"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="3"/>
+    </row>
+    <row r="29" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B29" s="1">
+        <v>24</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G29" s="15"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="3"/>
+    </row>
+    <row r="30" spans="2:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="4">
+        <v>25</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G30" s="16"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="3"/>
+    </row>
+    <row r="31" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B31" s="1">
+        <v>26</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="I31" s="3"/>
+    </row>
+    <row r="32" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B32" s="1">
+        <v>27</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G32" s="15"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B33" s="1">
         <v>28</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="C33" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G33" s="15"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="4">
         <v>29</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="C34" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="15"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="1">
         <v>30</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="C35" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" s="16"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="3"/>
+    </row>
+    <row r="36" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B36" s="21">
         <v>31</v>
       </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="14">
-        <v>8</v>
-      </c>
-      <c r="C13" s="15" t="s">
+      <c r="C36" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="I36" s="22"/>
+    </row>
+    <row r="37" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B37" s="4">
         <v>32</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="C37" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G37" s="18"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="3"/>
+    </row>
+    <row r="38" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="1">
         <v>33</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="C38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G38" s="18"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B39" s="1">
         <v>34</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="C39" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" s="18"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="3"/>
+    </row>
+    <row r="40" spans="2:9" ht="81" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="1">
         <v>35</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="2">
-        <v>9</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="C40" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G40" s="19"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="3"/>
+    </row>
+    <row r="41" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="1">
         <v>36</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="C41" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="1">
         <v>37</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="C42" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G42" s="15"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="3"/>
+    </row>
+    <row r="43" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B43" s="1">
         <v>38</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="C43" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G43" s="15"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="3"/>
+    </row>
+    <row r="44" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="4">
         <v>39</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="2">
-        <v>10</v>
-      </c>
-      <c r="C15" s="9" t="s">
+      <c r="C44" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G44" s="15"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="3"/>
+    </row>
+    <row r="45" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="21">
         <v>40</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="C45" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G45" s="15"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" spans="2:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="21">
         <v>41</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="C46" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="G46" s="16"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="22"/>
+    </row>
+    <row r="47" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="1">
         <v>42</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="C47" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="H47" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B48" s="1">
         <v>43</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="14">
-        <v>11</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="C48" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G48" s="15"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="1">
         <v>44</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="C49" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="G49" s="15"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="1">
         <v>45</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="C50" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G50" s="15"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="3"/>
+    </row>
+    <row r="51" spans="2:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="4">
         <v>46</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="C51" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G51" s="16"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="3"/>
+    </row>
+    <row r="52" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B52" s="1">
         <v>47</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="2">
-        <v>12</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="C52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="H52" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="I52" s="3"/>
+    </row>
+    <row r="53" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="1">
         <v>48</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="C53" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G53" s="15"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="3"/>
+    </row>
+    <row r="54" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B54" s="1">
         <v>49</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="C54" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="G54" s="15"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B55" s="1">
         <v>50</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="C55" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G55" s="15"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="2:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="4">
         <v>51</v>
       </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="2">
-        <v>13</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="C56" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G56" s="16"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B57" s="4">
         <v>52</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="C57" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="H57" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="I57" s="3"/>
+    </row>
+    <row r="58" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B58" s="21">
         <v>53</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="C58" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="F58" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="G58" s="15"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="3"/>
+    </row>
+    <row r="59" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B59" s="1">
         <v>54</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="C59" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G59" s="15"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="3"/>
+    </row>
+    <row r="60" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B60" s="1">
         <v>55</v>
       </c>
-      <c r="G18" s="12"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="2">
-        <v>14</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="C60" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G60" s="15"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="3"/>
+    </row>
+    <row r="61" spans="2:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="1">
         <v>56</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="C61" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G61" s="16"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="3"/>
+    </row>
+    <row r="62" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B62" s="1">
         <v>57</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="C62" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="H62" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="I62" s="3"/>
+    </row>
+    <row r="63" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B63" s="1">
         <v>58</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="C63" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="G63" s="15"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="3"/>
+    </row>
+    <row r="64" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B64" s="4">
         <v>59</v>
       </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B20" s="2">
-        <v>15</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="C64" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="G64" s="15"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="3"/>
+    </row>
+    <row r="65" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B65" s="1">
         <v>60</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="C65" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F65" s="2">
+        <v>7483815182</v>
+      </c>
+      <c r="G65" s="15"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="3"/>
+    </row>
+    <row r="66" spans="2:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B66" s="1">
         <v>61</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="C66" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G66" s="15"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="3"/>
+    </row>
+    <row r="67" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B67" s="1">
         <v>62</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="C67" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="H67" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="I67" s="3"/>
+    </row>
+    <row r="68" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B68" s="1">
         <v>63</v>
       </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B21" s="2">
-        <v>16</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="C68" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G68" s="12"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="3"/>
+    </row>
+    <row r="69" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B69" s="4">
         <v>64</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="C69" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E69" s="8"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="3"/>
+    </row>
+    <row r="70" spans="2:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="6">
         <v>65</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="14">
-        <v>17</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="G22" s="17"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="23" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B23" s="2">
-        <v>18</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G23" s="17"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-    </row>
-    <row r="24" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="2">
-        <v>19</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="17"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-    </row>
-    <row r="25" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="2">
-        <v>20</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" s="18"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-    </row>
-    <row r="26" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="2">
-        <v>21</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-    </row>
-    <row r="27" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="2">
-        <v>22</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-    </row>
-    <row r="28" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="2">
-        <v>23</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="12"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-    </row>
-    <row r="29" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="2">
-        <v>24</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G29" s="12"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-    </row>
-    <row r="30" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="14">
-        <v>25</v>
-      </c>
-      <c r="C30" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="G30" s="13"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-    </row>
-    <row r="31" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="2">
-        <v>26</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-    </row>
-    <row r="32" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B32" s="2">
-        <v>27</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="G32" s="12"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-    </row>
-    <row r="33" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B33" s="2">
-        <v>28</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G33" s="12"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-    </row>
-    <row r="34" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B34" s="14">
-        <v>29</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="G34" s="12"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-    </row>
-    <row r="35" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B35" s="2">
-        <v>30</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G35" s="13"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-    </row>
-    <row r="36" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="5">
-        <v>31</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="G36" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-    </row>
-    <row r="37" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B37" s="14">
-        <v>32</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-    </row>
-    <row r="38" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B38" s="2">
-        <v>33</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G38" s="23"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-    </row>
-    <row r="39" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B39" s="2">
-        <v>34</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="G39" s="23"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-    </row>
-    <row r="40" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B40" s="2">
-        <v>35</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="G40" s="24"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-    </row>
-    <row r="41" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="2">
-        <v>36</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-    </row>
-    <row r="42" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B42" s="2">
-        <v>37</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="G42" s="17"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-    </row>
-    <row r="43" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="2">
-        <v>38</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="G43" s="17"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="14">
-        <v>39</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="E44" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="G44" s="17"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-    </row>
-    <row r="45" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="7">
-        <v>40</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="G45" s="17"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-    </row>
-    <row r="46" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B46" s="5">
-        <v>41</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G46" s="18"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-    </row>
-    <row r="47" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="2">
-        <v>42</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="2">
-        <v>43</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G48" s="17"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="2">
-        <v>44</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G49" s="17"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-    </row>
-    <row r="50" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="2">
-        <v>45</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G50" s="17"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-    </row>
-    <row r="51" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="14">
-        <v>46</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>187</v>
-      </c>
-      <c r="G51" s="18"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-    </row>
-    <row r="52" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B52" s="2">
-        <v>47</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-    </row>
-    <row r="53" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="2">
-        <v>48</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G53" s="17"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-    </row>
-    <row r="54" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="2">
-        <v>49</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="G54" s="17"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-    </row>
-    <row r="55" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B55" s="2">
-        <v>50</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G55" s="17"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-    </row>
-    <row r="56" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="14">
-        <v>51</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>205</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F56" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="G56" s="18"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-    </row>
-    <row r="57" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="14">
-        <v>52</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="G57" s="11" t="s">
+      <c r="C70" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-    </row>
-    <row r="58" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="5">
-        <v>53</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="G58" s="12"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-    </row>
-    <row r="59" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B59" s="2">
-        <v>54</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G59" s="12"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-    </row>
-    <row r="60" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B60" s="2">
-        <v>55</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G60" s="12"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-    </row>
-    <row r="61" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B61" s="2">
-        <v>56</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G61" s="13"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-    </row>
-    <row r="62" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B62" s="2">
-        <v>57</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G62" s="11" t="s">
+      <c r="D70" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-    </row>
-    <row r="63" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B63" s="2">
-        <v>58</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G63" s="12"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-    </row>
-    <row r="64" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B64" s="14">
-        <v>59</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="E64" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="F64" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="G64" s="12"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-    </row>
-    <row r="65" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B65" s="2">
-        <v>60</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F65" s="3">
-        <v>7483815182</v>
-      </c>
-      <c r="G65" s="12"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-    </row>
-    <row r="66" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B66" s="2">
-        <v>61</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="G66" s="12"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-    </row>
-    <row r="67" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B67" s="2">
-        <v>62</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G67" s="25"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-    </row>
-    <row r="68" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B68" s="2">
-        <v>63</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G68" s="25"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-    </row>
-    <row r="69" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B69" s="14">
-        <v>64</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>269</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>270</v>
-      </c>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-    </row>
-    <row r="70" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B70" s="20">
-        <v>65</v>
-      </c>
-      <c r="C70" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="25"/>
+      <c r="I70" s="3"/>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D72" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="73" spans="2:11" ht="123" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="C73" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="D73" s="28" t="s">
-        <v>275</v>
-      </c>
-      <c r="E73" s="28"/>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
-      <c r="H73" s="28"/>
-      <c r="I73" s="28"/>
-      <c r="J73" s="28"/>
-      <c r="K73" s="28"/>
+      <c r="C73" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E73" s="10"/>
+      <c r="F73" s="10"/>
+      <c r="G73" s="10"/>
+      <c r="H73" s="10"/>
+      <c r="I73" s="10"/>
+      <c r="J73" s="10"/>
+      <c r="K73" s="10"/>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D74" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="27">
+    <mergeCell ref="H52:H56"/>
+    <mergeCell ref="H57:H61"/>
+    <mergeCell ref="H62:H66"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="H11:H15"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="H21:H25"/>
+    <mergeCell ref="H26:H30"/>
+    <mergeCell ref="H31:H35"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="G11:G15"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G26:G30"/>
     <mergeCell ref="D73:K73"/>
     <mergeCell ref="G41:G46"/>
     <mergeCell ref="G36:G40"/>
@@ -2737,12 +3090,10 @@
     <mergeCell ref="G52:G56"/>
     <mergeCell ref="G57:G61"/>
     <mergeCell ref="G62:G66"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="G11:G15"/>
-    <mergeCell ref="G16:G20"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="G67:G70"/>
+    <mergeCell ref="H36:H40"/>
+    <mergeCell ref="H41:H46"/>
+    <mergeCell ref="H47:H51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MINI PROJECT/3IST01_Mini Project Details.xlsx
+++ b/MINI PROJECT/3IST01_Mini Project Details.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="294">
   <si>
     <t>SI.NO</t>
   </si>
@@ -935,6 +935,12 @@
   </si>
   <si>
     <t>G2 Library Module</t>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>abs</t>
   </si>
 </sst>
 </file>
@@ -1291,50 +1297,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1360,17 +1327,26 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1382,6 +1358,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1673,55 +1679,55 @@
   </cols>
   <sheetData>
     <row r="5" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="E5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="13" t="s">
         <v>4</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="H5" s="43" t="s">
+      <c r="H5" s="27" t="s">
         <v>273</v>
       </c>
       <c r="I5" s="3"/>
     </row>
     <row r="6" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="29">
+      <c r="B6" s="16">
         <v>1</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="39" t="s">
+      <c r="G6" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="I6" s="42"/>
+      <c r="I6" s="26"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="32">
+      <c r="B7" s="19">
         <v>2</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1733,15 +1739,15 @@
       <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="33" t="s">
+      <c r="F7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="40"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="42"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="34">
+      <c r="B8" s="21">
         <v>3</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -1753,15 +1759,15 @@
       <c r="E8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="40"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="42"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="26"/>
     </row>
     <row r="9" spans="2:9" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="32">
+      <c r="B9" s="19">
         <v>4</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1773,53 +1779,53 @@
       <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="33" t="s">
+      <c r="F9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="40"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="42"/>
+      <c r="G9" s="39"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="36">
+      <c r="B10" s="23">
         <v>5</v>
       </c>
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="38" t="s">
+      <c r="F10" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="41"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="42"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="27">
+      <c r="B11" s="14">
         <v>6</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="28" t="s">
+      <c r="F11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="H11" s="47" t="s">
+      <c r="H11" s="37" t="s">
         <v>275</v>
       </c>
       <c r="I11" s="3"/>
@@ -1840,8 +1846,8 @@
       <c r="F12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="24"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="29"/>
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1860,8 +1866,8 @@
       <c r="F13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="24"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="29"/>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="2:9" ht="69" customHeight="1" x14ac:dyDescent="0.25">
@@ -1880,28 +1886,28 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="15"/>
-      <c r="H14" s="24"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="29"/>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>10</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="10" t="s">
         <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="25"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="30"/>
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1920,10 +1926,10 @@
       <c r="F16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="31" t="s">
         <v>258</v>
       </c>
-      <c r="H16" s="23" t="s">
+      <c r="H16" s="28" t="s">
         <v>276</v>
       </c>
       <c r="I16" s="3"/>
@@ -1944,8 +1950,8 @@
       <c r="F17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="24"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="29"/>
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1964,8 +1970,8 @@
       <c r="F18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="15"/>
-      <c r="H18" s="24"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="29"/>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1984,8 +1990,8 @@
       <c r="F19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="24"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="29"/>
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2004,8 +2010,8 @@
       <c r="F20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="25"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="30"/>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2024,10 +2030,10 @@
       <c r="F21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="31" t="s">
         <v>259</v>
       </c>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="28" t="s">
         <v>277</v>
       </c>
       <c r="I21" s="3"/>
@@ -2048,8 +2054,8 @@
       <c r="F22" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="15"/>
-      <c r="H22" s="24"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="29"/>
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2068,8 +2074,8 @@
       <c r="F23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="24"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="29"/>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2088,8 +2094,8 @@
       <c r="F24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="15"/>
-      <c r="H24" s="24"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="29"/>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2108,30 +2114,30 @@
       <c r="F25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="25"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="30"/>
       <c r="I25" s="3"/>
     </row>
     <row r="26" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
         <v>21</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="10" t="s">
         <v>86</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="28" t="s">
         <v>278</v>
       </c>
       <c r="I26" s="3"/>
@@ -2152,8 +2158,8 @@
       <c r="F27" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="15"/>
-      <c r="H27" s="24"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="29"/>
       <c r="I27" s="3"/>
     </row>
     <row r="28" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2172,8 +2178,8 @@
       <c r="F28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="24"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="29"/>
       <c r="I28" s="3"/>
     </row>
     <row r="29" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2192,8 +2198,8 @@
       <c r="F29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G29" s="15"/>
-      <c r="H29" s="24"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="29"/>
       <c r="I29" s="3"/>
     </row>
     <row r="30" spans="2:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2212,8 +2218,8 @@
       <c r="F30" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G30" s="16"/>
-      <c r="H30" s="25"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="30"/>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2232,10 +2238,10 @@
       <c r="F31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="H31" s="28" t="s">
         <v>279</v>
       </c>
       <c r="I31" s="3"/>
@@ -2244,21 +2250,23 @@
       <c r="B32" s="1">
         <v>27</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="10" t="s">
         <v>110</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="15"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="3"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="3" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="33" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
@@ -2276,9 +2284,11 @@
       <c r="F33" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="15"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="3"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="3" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="34" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="4">
@@ -2296,53 +2306,55 @@
       <c r="F34" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G34" s="15"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="3"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="3" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="35" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>30</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="D35" s="20" t="s">
+      <c r="D35" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="10" t="s">
         <v>122</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G35" s="16"/>
-      <c r="H35" s="25"/>
+      <c r="G35" s="33"/>
+      <c r="H35" s="30"/>
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B36" s="21">
+      <c r="B36" s="11">
         <v>31</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="F36" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="G36" s="17" t="s">
+      <c r="G36" s="42" t="s">
         <v>262</v>
       </c>
-      <c r="H36" s="23" t="s">
+      <c r="H36" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="I36" s="22"/>
+      <c r="I36" s="12"/>
     </row>
     <row r="37" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
@@ -2360,8 +2372,8 @@
       <c r="F37" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G37" s="18"/>
-      <c r="H37" s="24"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="29"/>
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2380,8 +2392,8 @@
       <c r="F38" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="18"/>
-      <c r="H38" s="24"/>
+      <c r="G38" s="43"/>
+      <c r="H38" s="29"/>
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2400,8 +2412,8 @@
       <c r="F39" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G39" s="18"/>
-      <c r="H39" s="24"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="29"/>
       <c r="I39" s="3"/>
     </row>
     <row r="40" spans="2:9" ht="81" customHeight="1" x14ac:dyDescent="0.25">
@@ -2420,8 +2432,8 @@
       <c r="F40" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="19"/>
-      <c r="H40" s="25"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="30"/>
       <c r="I40" s="3"/>
     </row>
     <row r="41" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2440,10 +2452,10 @@
       <c r="F41" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="H41" s="23" t="s">
+      <c r="H41" s="28" t="s">
         <v>281</v>
       </c>
       <c r="I41" s="3"/>
@@ -2464,8 +2476,8 @@
       <c r="F42" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G42" s="15"/>
-      <c r="H42" s="24"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="29"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2484,8 +2496,8 @@
       <c r="F43" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G43" s="15"/>
-      <c r="H43" s="24"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="29"/>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2504,49 +2516,49 @@
       <c r="F44" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G44" s="15"/>
-      <c r="H44" s="24"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="29"/>
       <c r="I44" s="3"/>
     </row>
     <row r="45" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="21">
+      <c r="B45" s="11">
         <v>40</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="F45" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="G45" s="15"/>
-      <c r="H45" s="24"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="29"/>
       <c r="I45" s="3"/>
     </row>
     <row r="46" spans="2:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="21">
+      <c r="B46" s="11">
         <v>41</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="F46" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="G46" s="16"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="22"/>
+      <c r="G46" s="33"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="12"/>
     </row>
     <row r="47" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
@@ -2564,10 +2576,10 @@
       <c r="F47" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="H47" s="23" t="s">
+      <c r="H47" s="28" t="s">
         <v>282</v>
       </c>
       <c r="I47" s="3"/>
@@ -2588,8 +2600,8 @@
       <c r="F48" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G48" s="15"/>
-      <c r="H48" s="24"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="29"/>
       <c r="I48" s="3"/>
     </row>
     <row r="49" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2608,8 +2620,8 @@
       <c r="F49" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G49" s="15"/>
-      <c r="H49" s="24"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="29"/>
       <c r="I49" s="3"/>
     </row>
     <row r="50" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2628,8 +2640,8 @@
       <c r="F50" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G50" s="15"/>
-      <c r="H50" s="24"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="29"/>
       <c r="I50" s="3"/>
     </row>
     <row r="51" spans="2:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2648,8 +2660,8 @@
       <c r="F51" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="G51" s="16"/>
-      <c r="H51" s="25"/>
+      <c r="G51" s="33"/>
+      <c r="H51" s="30"/>
       <c r="I51" s="3"/>
     </row>
     <row r="52" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2668,10 +2680,10 @@
       <c r="F52" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="G52" s="14" t="s">
+      <c r="G52" s="31" t="s">
         <v>264</v>
       </c>
-      <c r="H52" s="23" t="s">
+      <c r="H52" s="28" t="s">
         <v>283</v>
       </c>
       <c r="I52" s="3"/>
@@ -2692,28 +2704,28 @@
       <c r="F53" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G53" s="15"/>
-      <c r="H53" s="24"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="29"/>
       <c r="I53" s="3"/>
     </row>
     <row r="54" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B54" s="1">
         <v>49</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="10" t="s">
         <v>198</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="G54" s="15"/>
-      <c r="H54" s="24"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="29"/>
       <c r="I54" s="3"/>
     </row>
     <row r="55" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2732,8 +2744,8 @@
       <c r="F55" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G55" s="15"/>
-      <c r="H55" s="24"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="29"/>
       <c r="I55" s="3"/>
     </row>
     <row r="56" spans="2:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2752,8 +2764,8 @@
       <c r="F56" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G56" s="16"/>
-      <c r="H56" s="25"/>
+      <c r="G56" s="33"/>
+      <c r="H56" s="30"/>
       <c r="I56" s="3"/>
     </row>
     <row r="57" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2772,32 +2784,32 @@
       <c r="F57" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G57" s="14" t="s">
+      <c r="G57" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="H57" s="23" t="s">
+      <c r="H57" s="28" t="s">
         <v>284</v>
       </c>
       <c r="I57" s="3"/>
     </row>
     <row r="58" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="21">
+      <c r="B58" s="11">
         <v>53</v>
       </c>
-      <c r="C58" s="20" t="s">
+      <c r="C58" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="E58" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="F58" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="G58" s="15"/>
-      <c r="H58" s="24"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="29"/>
       <c r="I58" s="3"/>
     </row>
     <row r="59" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2816,8 +2828,8 @@
       <c r="F59" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G59" s="15"/>
-      <c r="H59" s="24"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="29"/>
       <c r="I59" s="3"/>
     </row>
     <row r="60" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2836,8 +2848,8 @@
       <c r="F60" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G60" s="15"/>
-      <c r="H60" s="24"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="29"/>
       <c r="I60" s="3"/>
     </row>
     <row r="61" spans="2:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2856,8 +2868,8 @@
       <c r="F61" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="G61" s="16"/>
-      <c r="H61" s="25"/>
+      <c r="G61" s="33"/>
+      <c r="H61" s="30"/>
       <c r="I61" s="3"/>
     </row>
     <row r="62" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2876,10 +2888,10 @@
       <c r="F62" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="G62" s="14" t="s">
+      <c r="G62" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="H62" s="23" t="s">
+      <c r="H62" s="28" t="s">
         <v>285</v>
       </c>
       <c r="I62" s="3"/>
@@ -2900,8 +2912,8 @@
       <c r="F63" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G63" s="15"/>
-      <c r="H63" s="24"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="29"/>
       <c r="I63" s="3"/>
     </row>
     <row r="64" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2920,8 +2932,8 @@
       <c r="F64" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G64" s="15"/>
-      <c r="H64" s="24"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="29"/>
       <c r="I64" s="3"/>
     </row>
     <row r="65" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2940,8 +2952,8 @@
       <c r="F65" s="2">
         <v>7483815182</v>
       </c>
-      <c r="G65" s="15"/>
-      <c r="H65" s="24"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="29"/>
       <c r="I65" s="3"/>
     </row>
     <row r="66" spans="2:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2960,8 +2972,8 @@
       <c r="F66" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="G66" s="15"/>
-      <c r="H66" s="25"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="30"/>
       <c r="I66" s="3"/>
     </row>
     <row r="67" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2980,10 +2992,10 @@
       <c r="F67" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="G67" s="11" t="s">
+      <c r="G67" s="45" t="s">
         <v>290</v>
       </c>
-      <c r="H67" s="23" t="s">
+      <c r="H67" s="28" t="s">
         <v>286</v>
       </c>
       <c r="I67" s="3"/>
@@ -3004,8 +3016,8 @@
       <c r="F68" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G68" s="12"/>
-      <c r="H68" s="24"/>
+      <c r="G68" s="46"/>
+      <c r="H68" s="29"/>
       <c r="I68" s="3"/>
     </row>
     <row r="69" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3020,8 +3032,8 @@
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="24"/>
+      <c r="G69" s="46"/>
+      <c r="H69" s="29"/>
       <c r="I69" s="3"/>
     </row>
     <row r="70" spans="2:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3036,8 +3048,8 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="25"/>
+      <c r="G70" s="47"/>
+      <c r="H70" s="30"/>
       <c r="I70" s="3"/>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
@@ -3049,16 +3061,16 @@
       <c r="C73" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D73" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="10"/>
-      <c r="I73" s="10"/>
-      <c r="J73" s="10"/>
-      <c r="K73" s="10"/>
+      <c r="E73" s="41"/>
+      <c r="F73" s="41"/>
+      <c r="G73" s="41"/>
+      <c r="H73" s="41"/>
+      <c r="I73" s="41"/>
+      <c r="J73" s="41"/>
+      <c r="K73" s="41"/>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D74" t="s">
@@ -3067,22 +3079,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="H52:H56"/>
-    <mergeCell ref="H57:H61"/>
-    <mergeCell ref="H62:H66"/>
-    <mergeCell ref="H67:H70"/>
-    <mergeCell ref="G31:G35"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="H11:H15"/>
-    <mergeCell ref="H16:H20"/>
-    <mergeCell ref="H21:H25"/>
-    <mergeCell ref="H26:H30"/>
-    <mergeCell ref="H31:H35"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="G11:G15"/>
-    <mergeCell ref="G16:G20"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G26:G30"/>
     <mergeCell ref="D73:K73"/>
     <mergeCell ref="G41:G46"/>
     <mergeCell ref="G36:G40"/>
@@ -3094,6 +3090,22 @@
     <mergeCell ref="H36:H40"/>
     <mergeCell ref="H41:H46"/>
     <mergeCell ref="H47:H51"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="G11:G15"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G26:G30"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="H11:H15"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="H21:H25"/>
+    <mergeCell ref="H26:H30"/>
+    <mergeCell ref="H52:H56"/>
+    <mergeCell ref="H57:H61"/>
+    <mergeCell ref="H62:H66"/>
+    <mergeCell ref="H67:H70"/>
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="H31:H35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MINI PROJECT/3IST01_Mini Project Details.xlsx
+++ b/MINI PROJECT/3IST01_Mini Project Details.xlsx
@@ -1329,14 +1329,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1346,30 +1340,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1388,6 +1358,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1718,10 +1718,10 @@
       <c r="F6" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="44" t="s">
         <v>274</v>
       </c>
       <c r="I6" s="26"/>
@@ -1742,8 +1742,8 @@
       <c r="F7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="39"/>
-      <c r="H7" s="35"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="45"/>
       <c r="I7" s="26"/>
     </row>
     <row r="8" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1762,8 +1762,8 @@
       <c r="F8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="39"/>
-      <c r="H8" s="35"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="45"/>
       <c r="I8" s="26"/>
     </row>
     <row r="9" spans="2:9" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1782,8 +1782,8 @@
       <c r="F9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="39"/>
-      <c r="H9" s="35"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="45"/>
       <c r="I9" s="26"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1802,8 +1802,8 @@
       <c r="F10" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="40"/>
-      <c r="H10" s="36"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="46"/>
       <c r="I10" s="26"/>
     </row>
     <row r="11" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1822,10 +1822,10 @@
       <c r="F11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="47" t="s">
         <v>275</v>
       </c>
       <c r="I11" s="3"/>
@@ -1846,8 +1846,8 @@
       <c r="F12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="39"/>
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1866,8 +1866,8 @@
       <c r="F13" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="32"/>
-      <c r="H13" s="29"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="39"/>
       <c r="I13" s="3"/>
     </row>
     <row r="14" spans="2:9" ht="69" customHeight="1" x14ac:dyDescent="0.25">
@@ -1886,8 +1886,8 @@
       <c r="F14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="29"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="39"/>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1906,8 +1906,8 @@
       <c r="F15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="33"/>
-      <c r="H15" s="30"/>
+      <c r="G15" s="31"/>
+      <c r="H15" s="40"/>
       <c r="I15" s="3"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1926,10 +1926,10 @@
       <c r="F16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="H16" s="28" t="s">
+      <c r="H16" s="38" t="s">
         <v>276</v>
       </c>
       <c r="I16" s="3"/>
@@ -1950,8 +1950,8 @@
       <c r="F17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="29"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="39"/>
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1970,8 +1970,8 @@
       <c r="F18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="29"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="39"/>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1990,8 +1990,8 @@
       <c r="F19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="29"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="39"/>
       <c r="I19" s="3"/>
     </row>
     <row r="20" spans="2:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2010,8 +2010,8 @@
       <c r="F20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G20" s="33"/>
-      <c r="H20" s="30"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="40"/>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2030,10 +2030,10 @@
       <c r="F21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="H21" s="38" t="s">
         <v>277</v>
       </c>
       <c r="I21" s="3"/>
@@ -2054,8 +2054,8 @@
       <c r="F22" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="32"/>
-      <c r="H22" s="29"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="39"/>
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2074,8 +2074,8 @@
       <c r="F23" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G23" s="32"/>
-      <c r="H23" s="29"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="39"/>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2094,8 +2094,8 @@
       <c r="F24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="32"/>
-      <c r="H24" s="29"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="39"/>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2114,8 +2114,8 @@
       <c r="F25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="G25" s="33"/>
-      <c r="H25" s="30"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="40"/>
       <c r="I25" s="3"/>
     </row>
     <row r="26" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2134,10 +2134,10 @@
       <c r="F26" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G26" s="31" t="s">
+      <c r="G26" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="H26" s="28" t="s">
+      <c r="H26" s="38" t="s">
         <v>278</v>
       </c>
       <c r="I26" s="3"/>
@@ -2158,8 +2158,8 @@
       <c r="F27" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="32"/>
-      <c r="H27" s="29"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="39"/>
       <c r="I27" s="3"/>
     </row>
     <row r="28" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2178,8 +2178,8 @@
       <c r="F28" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G28" s="32"/>
-      <c r="H28" s="29"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="39"/>
       <c r="I28" s="3"/>
     </row>
     <row r="29" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2198,8 +2198,8 @@
       <c r="F29" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G29" s="32"/>
-      <c r="H29" s="29"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="39"/>
       <c r="I29" s="3"/>
     </row>
     <row r="30" spans="2:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2218,8 +2218,8 @@
       <c r="F30" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G30" s="33"/>
-      <c r="H30" s="30"/>
+      <c r="G30" s="31"/>
+      <c r="H30" s="40"/>
       <c r="I30" s="3"/>
     </row>
     <row r="31" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2238,10 +2238,10 @@
       <c r="F31" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="29" t="s">
         <v>261</v>
       </c>
-      <c r="H31" s="28" t="s">
+      <c r="H31" s="38" t="s">
         <v>279</v>
       </c>
       <c r="I31" s="3"/>
@@ -2262,8 +2262,8 @@
       <c r="F32" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G32" s="32"/>
-      <c r="H32" s="29"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="39"/>
       <c r="I32" s="3" t="s">
         <v>293</v>
       </c>
@@ -2284,8 +2284,8 @@
       <c r="F33" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="G33" s="32"/>
-      <c r="H33" s="29"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="39"/>
       <c r="I33" s="3" t="s">
         <v>293</v>
       </c>
@@ -2306,8 +2306,8 @@
       <c r="F34" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="29"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="39"/>
       <c r="I34" s="3" t="s">
         <v>292</v>
       </c>
@@ -2328,8 +2328,8 @@
       <c r="F35" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G35" s="33"/>
-      <c r="H35" s="30"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="40"/>
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2348,10 +2348,10 @@
       <c r="F36" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="G36" s="42" t="s">
+      <c r="G36" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="H36" s="28" t="s">
+      <c r="H36" s="38" t="s">
         <v>280</v>
       </c>
       <c r="I36" s="12"/>
@@ -2372,8 +2372,8 @@
       <c r="F37" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="G37" s="43"/>
-      <c r="H37" s="29"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="39"/>
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2392,8 +2392,8 @@
       <c r="F38" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G38" s="43"/>
-      <c r="H38" s="29"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="39"/>
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2412,8 +2412,8 @@
       <c r="F39" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G39" s="43"/>
-      <c r="H39" s="29"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="39"/>
       <c r="I39" s="3"/>
     </row>
     <row r="40" spans="2:9" ht="81" customHeight="1" x14ac:dyDescent="0.25">
@@ -2432,8 +2432,8 @@
       <c r="F40" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G40" s="44"/>
-      <c r="H40" s="30"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="40"/>
       <c r="I40" s="3"/>
     </row>
     <row r="41" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2452,10 +2452,10 @@
       <c r="F41" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="H41" s="28" t="s">
+      <c r="H41" s="38" t="s">
         <v>281</v>
       </c>
       <c r="I41" s="3"/>
@@ -2476,8 +2476,8 @@
       <c r="F42" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="G42" s="32"/>
-      <c r="H42" s="29"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="39"/>
       <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2496,8 +2496,8 @@
       <c r="F43" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G43" s="32"/>
-      <c r="H43" s="29"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="39"/>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2516,8 +2516,8 @@
       <c r="F44" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="G44" s="32"/>
-      <c r="H44" s="29"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="39"/>
       <c r="I44" s="3"/>
     </row>
     <row r="45" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
@@ -2536,8 +2536,8 @@
       <c r="F45" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="G45" s="32"/>
-      <c r="H45" s="29"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="39"/>
       <c r="I45" s="3"/>
     </row>
     <row r="46" spans="2:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2556,8 +2556,8 @@
       <c r="F46" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="G46" s="33"/>
-      <c r="H46" s="30"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="40"/>
       <c r="I46" s="12"/>
     </row>
     <row r="47" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2576,10 +2576,10 @@
       <c r="F47" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="G47" s="31" t="s">
+      <c r="G47" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="H47" s="28" t="s">
+      <c r="H47" s="38" t="s">
         <v>282</v>
       </c>
       <c r="I47" s="3"/>
@@ -2600,8 +2600,8 @@
       <c r="F48" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="G48" s="32"/>
-      <c r="H48" s="29"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="39"/>
       <c r="I48" s="3"/>
     </row>
     <row r="49" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2620,8 +2620,8 @@
       <c r="F49" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="G49" s="32"/>
-      <c r="H49" s="29"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="39"/>
       <c r="I49" s="3"/>
     </row>
     <row r="50" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2640,8 +2640,8 @@
       <c r="F50" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="G50" s="32"/>
-      <c r="H50" s="29"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="39"/>
       <c r="I50" s="3"/>
     </row>
     <row r="51" spans="2:9" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2660,8 +2660,8 @@
       <c r="F51" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="G51" s="33"/>
-      <c r="H51" s="30"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="40"/>
       <c r="I51" s="3"/>
     </row>
     <row r="52" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2680,10 +2680,10 @@
       <c r="F52" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="G52" s="31" t="s">
+      <c r="G52" s="29" t="s">
         <v>264</v>
       </c>
-      <c r="H52" s="28" t="s">
+      <c r="H52" s="38" t="s">
         <v>283</v>
       </c>
       <c r="I52" s="3"/>
@@ -2704,8 +2704,8 @@
       <c r="F53" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="G53" s="32"/>
-      <c r="H53" s="29"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="39"/>
       <c r="I53" s="3"/>
     </row>
     <row r="54" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2724,8 +2724,8 @@
       <c r="F54" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="G54" s="32"/>
-      <c r="H54" s="29"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="39"/>
       <c r="I54" s="3"/>
     </row>
     <row r="55" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2744,8 +2744,8 @@
       <c r="F55" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="G55" s="32"/>
-      <c r="H55" s="29"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="39"/>
       <c r="I55" s="3"/>
     </row>
     <row r="56" spans="2:9" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2764,8 +2764,8 @@
       <c r="F56" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G56" s="33"/>
-      <c r="H56" s="30"/>
+      <c r="G56" s="31"/>
+      <c r="H56" s="40"/>
       <c r="I56" s="3"/>
     </row>
     <row r="57" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2784,10 +2784,10 @@
       <c r="F57" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G57" s="31" t="s">
+      <c r="G57" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="H57" s="28" t="s">
+      <c r="H57" s="38" t="s">
         <v>284</v>
       </c>
       <c r="I57" s="3"/>
@@ -2808,8 +2808,8 @@
       <c r="F58" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="G58" s="32"/>
-      <c r="H58" s="29"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="39"/>
       <c r="I58" s="3"/>
     </row>
     <row r="59" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2828,8 +2828,8 @@
       <c r="F59" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G59" s="32"/>
-      <c r="H59" s="29"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="39"/>
       <c r="I59" s="3"/>
     </row>
     <row r="60" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2848,8 +2848,8 @@
       <c r="F60" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G60" s="32"/>
-      <c r="H60" s="29"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="39"/>
       <c r="I60" s="3"/>
     </row>
     <row r="61" spans="2:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2868,8 +2868,8 @@
       <c r="F61" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="G61" s="33"/>
-      <c r="H61" s="30"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="40"/>
       <c r="I61" s="3"/>
     </row>
     <row r="62" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2888,10 +2888,10 @@
       <c r="F62" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="G62" s="31" t="s">
+      <c r="G62" s="29" t="s">
         <v>289</v>
       </c>
-      <c r="H62" s="28" t="s">
+      <c r="H62" s="38" t="s">
         <v>285</v>
       </c>
       <c r="I62" s="3"/>
@@ -2912,8 +2912,8 @@
       <c r="F63" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="G63" s="32"/>
-      <c r="H63" s="29"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="39"/>
       <c r="I63" s="3"/>
     </row>
     <row r="64" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -2932,8 +2932,8 @@
       <c r="F64" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G64" s="32"/>
-      <c r="H64" s="29"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="39"/>
       <c r="I64" s="3"/>
     </row>
     <row r="65" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2952,8 +2952,8 @@
       <c r="F65" s="2">
         <v>7483815182</v>
       </c>
-      <c r="G65" s="32"/>
-      <c r="H65" s="29"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="39"/>
       <c r="I65" s="3"/>
     </row>
     <row r="66" spans="2:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2972,8 +2972,8 @@
       <c r="F66" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="G66" s="32"/>
-      <c r="H66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="40"/>
       <c r="I66" s="3"/>
     </row>
     <row r="67" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -2992,10 +2992,10 @@
       <c r="F67" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="G67" s="45" t="s">
+      <c r="G67" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="H67" s="28" t="s">
+      <c r="H67" s="38" t="s">
         <v>286</v>
       </c>
       <c r="I67" s="3"/>
@@ -3016,8 +3016,8 @@
       <c r="F68" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G68" s="46"/>
-      <c r="H68" s="29"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="39"/>
       <c r="I68" s="3"/>
     </row>
     <row r="69" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -3032,8 +3032,8 @@
       </c>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
-      <c r="G69" s="46"/>
-      <c r="H69" s="29"/>
+      <c r="G69" s="36"/>
+      <c r="H69" s="39"/>
       <c r="I69" s="3"/>
     </row>
     <row r="70" spans="2:11" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3048,8 +3048,8 @@
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="30"/>
+      <c r="G70" s="37"/>
+      <c r="H70" s="40"/>
       <c r="I70" s="3"/>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.25">
@@ -3061,16 +3061,16 @@
       <c r="C73" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="D73" s="41" t="s">
+      <c r="D73" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="E73" s="41"/>
-      <c r="F73" s="41"/>
-      <c r="G73" s="41"/>
-      <c r="H73" s="41"/>
-      <c r="I73" s="41"/>
-      <c r="J73" s="41"/>
-      <c r="K73" s="41"/>
+      <c r="E73" s="28"/>
+      <c r="F73" s="28"/>
+      <c r="G73" s="28"/>
+      <c r="H73" s="28"/>
+      <c r="I73" s="28"/>
+      <c r="J73" s="28"/>
+      <c r="K73" s="28"/>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D74" t="s">
@@ -3079,6 +3079,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="G31:G35"/>
+    <mergeCell ref="H31:H35"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="H11:H15"/>
+    <mergeCell ref="H16:H20"/>
+    <mergeCell ref="H21:H25"/>
+    <mergeCell ref="H26:H30"/>
+    <mergeCell ref="G6:G10"/>
+    <mergeCell ref="G11:G15"/>
+    <mergeCell ref="G16:G20"/>
+    <mergeCell ref="G21:G25"/>
+    <mergeCell ref="G26:G30"/>
     <mergeCell ref="D73:K73"/>
     <mergeCell ref="G41:G46"/>
     <mergeCell ref="G36:G40"/>
@@ -3090,22 +3102,10 @@
     <mergeCell ref="H36:H40"/>
     <mergeCell ref="H41:H46"/>
     <mergeCell ref="H47:H51"/>
-    <mergeCell ref="G6:G10"/>
-    <mergeCell ref="G11:G15"/>
-    <mergeCell ref="G16:G20"/>
-    <mergeCell ref="G21:G25"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="H11:H15"/>
-    <mergeCell ref="H16:H20"/>
-    <mergeCell ref="H21:H25"/>
-    <mergeCell ref="H26:H30"/>
     <mergeCell ref="H52:H56"/>
     <mergeCell ref="H57:H61"/>
     <mergeCell ref="H62:H66"/>
     <mergeCell ref="H67:H70"/>
-    <mergeCell ref="G31:G35"/>
-    <mergeCell ref="H31:H35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MINI PROJECT/3IST01_Mini Project Details.xlsx
+++ b/MINI PROJECT/3IST01_Mini Project Details.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="301">
   <si>
     <t>SI.NO</t>
   </si>
@@ -941,6 +941,27 @@
   </si>
   <si>
     <t>abs</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Incomplete</t>
+  </si>
+  <si>
+    <t>Rejected</t>
+  </si>
+  <si>
+    <t>absent</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>left college</t>
   </si>
 </sst>
 </file>
@@ -1368,15 +1389,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1388,6 +1400,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1676,6 +1697,7 @@
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" customWidth="1"/>
     <col min="8" max="8" width="79.85546875" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1718,10 +1740,10 @@
       <c r="F6" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="45" t="s">
         <v>257</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="41" t="s">
         <v>274</v>
       </c>
       <c r="I6" s="26"/>
@@ -1742,8 +1764,8 @@
       <c r="F7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="42"/>
-      <c r="H7" s="45"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="42"/>
       <c r="I7" s="26"/>
     </row>
     <row r="8" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1762,9 +1784,11 @@
       <c r="F8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="26"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="26" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="9" spans="2:9" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="19">
@@ -1782,8 +1806,8 @@
       <c r="F9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="42"/>
-      <c r="H9" s="45"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="42"/>
       <c r="I9" s="26"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1802,8 +1826,8 @@
       <c r="F10" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="43"/>
-      <c r="H10" s="46"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="43"/>
       <c r="I10" s="26"/>
     </row>
     <row r="11" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
@@ -1825,7 +1849,7 @@
       <c r="G11" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="H11" s="47" t="s">
+      <c r="H11" s="44" t="s">
         <v>275</v>
       </c>
       <c r="I11" s="3"/>
@@ -1848,7 +1872,9 @@
       </c>
       <c r="G12" s="30"/>
       <c r="H12" s="39"/>
-      <c r="I12" s="3"/>
+      <c r="I12" s="3" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="13" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="4">
@@ -1952,7 +1978,9 @@
       </c>
       <c r="G17" s="30"/>
       <c r="H17" s="39"/>
-      <c r="I17" s="3"/>
+      <c r="I17" s="3" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="18" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
@@ -2036,7 +2064,9 @@
       <c r="H21" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="I21" s="3"/>
+      <c r="I21" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="22" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
@@ -2056,7 +2086,9 @@
       </c>
       <c r="G22" s="30"/>
       <c r="H22" s="39"/>
-      <c r="I22" s="3"/>
+      <c r="I22" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="23" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
@@ -2076,7 +2108,9 @@
       </c>
       <c r="G23" s="30"/>
       <c r="H23" s="39"/>
-      <c r="I23" s="3"/>
+      <c r="I23" s="3">
+        <v>25</v>
+      </c>
     </row>
     <row r="24" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
@@ -2096,7 +2130,9 @@
       </c>
       <c r="G24" s="30"/>
       <c r="H24" s="39"/>
-      <c r="I24" s="3"/>
+      <c r="I24" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="25" spans="2:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
@@ -2116,7 +2152,9 @@
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="40"/>
-      <c r="I25" s="3"/>
+      <c r="I25" s="3">
+        <v>17</v>
+      </c>
     </row>
     <row r="26" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="1">
@@ -2140,7 +2178,9 @@
       <c r="H26" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="I26" s="3"/>
+      <c r="I26" s="3">
+        <v>10</v>
+      </c>
     </row>
     <row r="27" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="1">
@@ -2160,7 +2200,9 @@
       </c>
       <c r="G27" s="30"/>
       <c r="H27" s="39"/>
-      <c r="I27" s="3"/>
+      <c r="I27" s="3">
+        <v>7</v>
+      </c>
     </row>
     <row r="28" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
@@ -2180,7 +2222,9 @@
       </c>
       <c r="G28" s="30"/>
       <c r="H28" s="39"/>
-      <c r="I28" s="3"/>
+      <c r="I28" s="3">
+        <v>9</v>
+      </c>
     </row>
     <row r="29" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
@@ -2200,7 +2244,9 @@
       </c>
       <c r="G29" s="30"/>
       <c r="H29" s="39"/>
-      <c r="I29" s="3"/>
+      <c r="I29" s="3">
+        <v>7</v>
+      </c>
     </row>
     <row r="30" spans="2:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
@@ -2220,7 +2266,9 @@
       </c>
       <c r="G30" s="31"/>
       <c r="H30" s="40"/>
-      <c r="I30" s="3"/>
+      <c r="I30" s="3" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="31" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
@@ -2354,7 +2402,9 @@
       <c r="H36" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="I36" s="12"/>
+      <c r="I36" s="12">
+        <v>15</v>
+      </c>
     </row>
     <row r="37" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
@@ -2374,7 +2424,9 @@
       </c>
       <c r="G37" s="33"/>
       <c r="H37" s="39"/>
-      <c r="I37" s="3"/>
+      <c r="I37" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="38" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1">
@@ -2394,7 +2446,9 @@
       </c>
       <c r="G38" s="33"/>
       <c r="H38" s="39"/>
-      <c r="I38" s="3"/>
+      <c r="I38" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="39" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B39" s="1">
@@ -2414,7 +2468,9 @@
       </c>
       <c r="G39" s="33"/>
       <c r="H39" s="39"/>
-      <c r="I39" s="3"/>
+      <c r="I39" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="40" spans="2:9" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="1">
@@ -2434,7 +2490,9 @@
       </c>
       <c r="G40" s="34"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="3"/>
+      <c r="I40" s="3" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="41" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1">
@@ -2458,7 +2516,9 @@
       <c r="H41" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="I41" s="3"/>
+      <c r="I41" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1">
@@ -2478,7 +2538,9 @@
       </c>
       <c r="G42" s="30"/>
       <c r="H42" s="39"/>
-      <c r="I42" s="3"/>
+      <c r="I42" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="43" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B43" s="1">
@@ -2498,7 +2560,9 @@
       </c>
       <c r="G43" s="30"/>
       <c r="H43" s="39"/>
-      <c r="I43" s="3"/>
+      <c r="I43" s="3" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="44" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B44" s="4">
@@ -2518,7 +2582,9 @@
       </c>
       <c r="G44" s="30"/>
       <c r="H44" s="39"/>
-      <c r="I44" s="3"/>
+      <c r="I44" s="3">
+        <v>20</v>
+      </c>
     </row>
     <row r="45" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="11">
@@ -2538,7 +2604,9 @@
       </c>
       <c r="G45" s="30"/>
       <c r="H45" s="39"/>
-      <c r="I45" s="3"/>
+      <c r="I45" s="3">
+        <v>10</v>
+      </c>
     </row>
     <row r="46" spans="2:9" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="11">
@@ -2558,7 +2626,9 @@
       </c>
       <c r="G46" s="31"/>
       <c r="H46" s="40"/>
-      <c r="I46" s="12"/>
+      <c r="I46" s="12" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="47" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B47" s="1">
@@ -2790,7 +2860,9 @@
       <c r="H57" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="I57" s="3"/>
+      <c r="I57" s="3">
+        <v>25</v>
+      </c>
     </row>
     <row r="58" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B58" s="11">
@@ -2810,7 +2882,9 @@
       </c>
       <c r="G58" s="30"/>
       <c r="H58" s="39"/>
-      <c r="I58" s="3"/>
+      <c r="I58" s="3" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="59" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B59" s="1">
@@ -2830,7 +2904,9 @@
       </c>
       <c r="G59" s="30"/>
       <c r="H59" s="39"/>
-      <c r="I59" s="3"/>
+      <c r="I59" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="60" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B60" s="1">
@@ -2850,7 +2926,9 @@
       </c>
       <c r="G60" s="30"/>
       <c r="H60" s="39"/>
-      <c r="I60" s="3"/>
+      <c r="I60" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="61" spans="2:9" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="1">
@@ -2870,7 +2948,9 @@
       </c>
       <c r="G61" s="31"/>
       <c r="H61" s="40"/>
-      <c r="I61" s="3"/>
+      <c r="I61" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="62" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B62" s="1">
@@ -2894,7 +2974,9 @@
       <c r="H62" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="I62" s="3"/>
+      <c r="I62" s="3">
+        <v>25</v>
+      </c>
     </row>
     <row r="63" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B63" s="1">
@@ -2914,7 +2996,9 @@
       </c>
       <c r="G63" s="30"/>
       <c r="H63" s="39"/>
-      <c r="I63" s="3"/>
+      <c r="I63" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="64" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B64" s="4">
@@ -2934,7 +3018,9 @@
       </c>
       <c r="G64" s="30"/>
       <c r="H64" s="39"/>
-      <c r="I64" s="3"/>
+      <c r="I64" s="3">
+        <v>15</v>
+      </c>
     </row>
     <row r="65" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
@@ -2954,7 +3040,9 @@
       </c>
       <c r="G65" s="30"/>
       <c r="H65" s="39"/>
-      <c r="I65" s="3"/>
+      <c r="I65" s="3">
+        <v>25</v>
+      </c>
     </row>
     <row r="66" spans="2:11" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="1">
@@ -2974,7 +3062,9 @@
       </c>
       <c r="G66" s="30"/>
       <c r="H66" s="40"/>
-      <c r="I66" s="3"/>
+      <c r="I66" s="3">
+        <v>23</v>
+      </c>
     </row>
     <row r="67" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B67" s="1">
